--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260827.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260827.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.05%</t>
+          <t>10.96%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.39%</t>
+          <t>10.40%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.06%</t>
+          <t>8.22%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.41%</t>
+          <t>7.46%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.56%</t>
+          <t>5.51%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.28%</t>
+          <t>4.24%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.42%</t>
+          <t>3.39%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.07%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.63%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.14%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.33%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
@@ -1129,44 +1129,44 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ACM UN</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>艾奕康</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>21,558</t>
+          <t>45,527</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>ACM UN</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>艾奕康</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>45,527</t>
+          <t>21,558</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
@@ -1188,24 +1188,24 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>DTE US</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>DTE能源</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>20,009</t>
+          <t>10,937</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>DTE US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>DTE能源</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>10,937</t>
+          <t>20,009</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1254,73 +1254,73 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>PPL公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>72,674</t>
+          <t>8,704</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>PPL公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>12,752</t>
+          <t>72,674</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>8,704</t>
+          <t>12,752</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1386,51 +1386,51 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>GNRC US</t>
+          <t>CMS US</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>基內瑞克控股公司</t>
+          <t>CMS能源</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>10,246</t>
+          <t>29,691</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>CMS US</t>
+          <t>GNRC US</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>CMS能源</t>
+          <t>基內瑞克控股公司</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>29,691</t>
+          <t>10,246</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>146,596,601</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
